--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.58374527274499</v>
+        <v>3.994858606821061</v>
       </c>
       <c r="D2" t="n">
-        <v>24.36279407070718</v>
+        <v>3.958954036489917</v>
       </c>
       <c r="E2" t="n">
-        <v>20.13848887782022</v>
+        <v>3.272504442645786</v>
       </c>
       <c r="F2" t="n">
-        <v>20.02574857144207</v>
+        <v>3.254184142859336</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.15090227615795</v>
+        <v>3.437021619875668</v>
       </c>
       <c r="D3" t="n">
-        <v>21.49138855714711</v>
+        <v>3.492350640536406</v>
       </c>
       <c r="E3" t="n">
-        <v>20.13848887782022</v>
+        <v>3.272504442645786</v>
       </c>
       <c r="F3" t="n">
-        <v>20.02574857144207</v>
+        <v>3.254184142859336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.48394020501746</v>
+        <v>10.64114028331534</v>
       </c>
       <c r="D4" t="n">
-        <v>65.33527447581568</v>
+        <v>10.61698210232005</v>
       </c>
       <c r="E4" t="n">
-        <v>20.13848887782022</v>
+        <v>3.272504442645786</v>
       </c>
       <c r="F4" t="n">
-        <v>20.02574857144207</v>
+        <v>3.254184142859336</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
